--- a/refs/heads/main/StructureDefinition-BundleTerminarLE.xlsx
+++ b/refs/heads/main/StructureDefinition-BundleTerminarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T21:42:45+00:00</t>
+    <t>2023-02-15T05:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-BundleTerminarLE.xlsx
+++ b/refs/heads/main/StructureDefinition-BundleTerminarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T05:04:04+00:00</t>
+    <t>2023-02-15T13:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-BundleTerminarLE.xlsx
+++ b/refs/heads/main/StructureDefinition-BundleTerminarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T13:37:26+00:00</t>
+    <t>2023-02-15T14:04:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-BundleTerminarLE.xlsx
+++ b/refs/heads/main/StructureDefinition-BundleTerminarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T14:04:38+00:00</t>
+    <t>2023-02-15T16:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-BundleTerminarLE.xlsx
+++ b/refs/heads/main/StructureDefinition-BundleTerminarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:11:45+00:00</t>
+    <t>2023-02-15T16:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-BundleTerminarLE.xlsx
+++ b/refs/heads/main/StructureDefinition-BundleTerminarLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:20:01+00:00</t>
+    <t>2023-02-20T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
